--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-assigned-entity.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-assigned-entity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="201">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -588,6 +588,9 @@
   </si>
   <si>
     <t>CD.translation</t>
+  </si>
+  <si>
+    <t>AssignedEntity.sdtcSpecialty</t>
   </si>
   <si>
     <t>AssignedEntity.addr</t>
@@ -945,7 +948,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK37"/>
+  <dimension ref="A1:AK38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="37.9375" customWidth="true" bestFit="true"/>
@@ -4187,11 +4190,9 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="L32" s="2"/>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4262,10 +4263,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4288,10 +4289,10 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
@@ -4343,7 +4344,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4363,10 +4364,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4377,7 +4378,7 @@
         <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>74</v>
@@ -4389,10 +4390,10 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
@@ -4444,13 +4445,13 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>74</v>
@@ -4464,10 +4465,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4490,10 +4491,10 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
@@ -4545,7 +4546,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4565,10 +4566,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4579,7 +4580,7 @@
         <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>74</v>
@@ -4591,9 +4592,11 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="L36" s="2"/>
+        <v>196</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>197</v>
+      </c>
       <c r="M36" s="2"/>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4644,7 +4647,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4664,10 +4667,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4675,10 +4678,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>74</v>
@@ -4690,7 +4693,7 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
@@ -4743,10 +4746,10 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>75</v>
@@ -4758,6 +4761,105 @@
         <v>74</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK38" t="s" s="2">
         <v>74</v>
       </c>
     </row>
